--- a/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
+++ b/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
@@ -550,13 +550,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.6741225709545156</v>
+        <v>0.6741225709545154</v>
       </c>
       <c r="C2">
-        <v>0.3705533249609645</v>
+        <v>0.3705533249609646</v>
       </c>
       <c r="D2">
-        <v>0.3035692459935511</v>
+        <v>0.3035692459935508</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -567,10 +567,10 @@
         <v>0.3118390881364234</v>
       </c>
       <c r="C3">
-        <v>0.402374055434859</v>
+        <v>0.4023740554348589</v>
       </c>
       <c r="D3">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -595,7 +595,7 @@
         <v>0.6867618794440014</v>
       </c>
       <c r="C5">
-        <v>0.337676499616521</v>
+        <v>0.3376764996165211</v>
       </c>
       <c r="D5">
         <v>0.3490853798274803</v>
@@ -626,7 +626,7 @@
         <v>0.5864783189261368</v>
       </c>
       <c r="D7">
-        <v>-0.325687326512341</v>
+        <v>-0.3256873265123409</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -634,10 +634,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.5951237281573062</v>
+        <v>0.5951237281573063</v>
       </c>
       <c r="C8">
-        <v>0.4041932886603292</v>
+        <v>0.4041932886603293</v>
       </c>
       <c r="D8">
         <v>0.190930439496977</v>
@@ -693,10 +693,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12">
-        <v>0.6293909101742615</v>
+        <v>0.6293909101742614</v>
       </c>
       <c r="D12">
-        <v>-0.3785271549791805</v>
+        <v>-0.3785271549791804</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -707,10 +707,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13">
-        <v>0.672915387130386</v>
+        <v>0.6729153871303859</v>
       </c>
       <c r="D13">
-        <v>-0.5012702603247939</v>
+        <v>-0.5012702603247938</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -732,13 +732,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.381623523649759</v>
+        <v>0.3816235236497591</v>
       </c>
       <c r="C15">
-        <v>0.5485467523459439</v>
+        <v>0.5485467523459437</v>
       </c>
       <c r="D15">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961846</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -746,13 +746,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>0.2828138579726733</v>
+        <v>0.2828138579726732</v>
       </c>
       <c r="C16">
         <v>0.4976624590930341</v>
       </c>
       <c r="D16">
-        <v>-0.2148486011203608</v>
+        <v>-0.2148486011203609</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -760,13 +760,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>0.2145524253023635</v>
+        <v>0.2145524253023634</v>
       </c>
       <c r="C17">
         <v>0.6001120644611281</v>
       </c>
       <c r="D17">
-        <v>-0.3855596391587646</v>
+        <v>-0.3855596391587647</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -774,13 +774,13 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>0.4296518046208667</v>
+        <v>0.4296518046208666</v>
       </c>
       <c r="C18">
-        <v>0.4945453559326178</v>
+        <v>0.4945453559326177</v>
       </c>
       <c r="D18">
-        <v>-0.06489355131175112</v>
+        <v>-0.06489355131175117</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -805,10 +805,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20">
-        <v>0.515004568135498</v>
+        <v>0.5150045681354979</v>
       </c>
       <c r="D20">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -816,7 +816,7 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>0.7118486478275275</v>
+        <v>0.7118486478275274</v>
       </c>
       <c r="C21">
         <v>0.4260034620050295</v>
@@ -858,13 +858,13 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>0.2175554342042255</v>
+        <v>0.2175554342042256</v>
       </c>
       <c r="C24">
-        <v>0.5970724973798153</v>
+        <v>0.5970724973798152</v>
       </c>
       <c r="D24">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -875,10 +875,10 @@
         <v>0.547386166559502</v>
       </c>
       <c r="C25">
-        <v>0.4276290460083051</v>
+        <v>0.4276290460083053</v>
       </c>
       <c r="D25">
-        <v>0.1197571205511969</v>
+        <v>0.1197571205511967</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -886,13 +886,13 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>0.2573693650749999</v>
+        <v>0.257369365075</v>
       </c>
       <c r="C26">
         <v>0.5837653200597678</v>
       </c>
       <c r="D26">
-        <v>-0.3263959549847679</v>
+        <v>-0.3263959549847678</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -903,10 +903,10 @@
         <v>0.1922848927634011</v>
       </c>
       <c r="C27">
-        <v>0.5332163798977594</v>
+        <v>0.5332163798977593</v>
       </c>
       <c r="D27">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -928,13 +928,13 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>0.3727681504267594</v>
+        <v>0.3727681504267595</v>
       </c>
       <c r="C29">
         <v>0.5189573803652675</v>
       </c>
       <c r="D29">
-        <v>-0.1461892299385081</v>
+        <v>-0.146189229938508</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -948,7 +948,7 @@
         <v>0.4250474383301707</v>
       </c>
       <c r="D30">
-        <v>-0.1957735252430408</v>
+        <v>-0.1957735252430409</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -956,7 +956,7 @@
         <v>33</v>
       </c>
       <c r="B31">
-        <v>0.2726179454172195</v>
+        <v>0.2726179454172194</v>
       </c>
       <c r="C31">
         <v>0.5623898070994021</v>
@@ -973,7 +973,7 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32">
-        <v>0.4830115777026098</v>
+        <v>0.4830115777026097</v>
       </c>
       <c r="D32">
         <v>-0.1405419733734229</v>
@@ -987,10 +987,10 @@
         <v>0.3328760832679651</v>
       </c>
       <c r="C33">
-        <v>0.4307152111273059</v>
+        <v>0.4307152111273058</v>
       </c>
       <c r="D33">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934062</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1012,10 +1012,10 @@
         <v>37</v>
       </c>
       <c r="B35">
-        <v>0.5394791234243425</v>
+        <v>0.5394791234243426</v>
       </c>
       <c r="C35">
-        <v>0.3857011247696834</v>
+        <v>0.3857011247696835</v>
       </c>
       <c r="D35">
         <v>0.1537779986546591</v>
@@ -1082,13 +1082,13 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>0.4653345520848202</v>
+        <v>0.4653345520848203</v>
       </c>
       <c r="C40">
         <v>0.4840879159829741</v>
       </c>
       <c r="D40">
-        <v>-0.01875336389815385</v>
+        <v>-0.0187533638981538</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1099,10 +1099,10 @@
         <v>0.6175455689522186</v>
       </c>
       <c r="C41">
-        <v>0.3789088878499818</v>
+        <v>0.3789088878499817</v>
       </c>
       <c r="D41">
-        <v>0.2386366811022367</v>
+        <v>0.2386366811022368</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1113,10 +1113,10 @@
         <v>0.5620888841745206</v>
       </c>
       <c r="C42">
-        <v>0.3852882355996785</v>
+        <v>0.3852882355996786</v>
       </c>
       <c r="D42">
-        <v>0.1768006485748422</v>
+        <v>0.1768006485748421</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1155,7 +1155,7 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C45">
-        <v>0.4177957142027763</v>
+        <v>0.4177957142027762</v>
       </c>
       <c r="D45">
         <v>-0.1253328976907889</v>
@@ -1166,7 +1166,7 @@
         <v>48</v>
       </c>
       <c r="B46">
-        <v>0.3383392939535171</v>
+        <v>0.3383392939535172</v>
       </c>
       <c r="C46">
         <v>0.5106782077019681</v>
@@ -1180,13 +1180,13 @@
         <v>49</v>
       </c>
       <c r="B47">
-        <v>0.604162001406453</v>
+        <v>0.6041620014064532</v>
       </c>
       <c r="C47">
         <v>0.3523044639392301</v>
       </c>
       <c r="D47">
-        <v>0.2518575374672229</v>
+        <v>0.2518575374672231</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1211,10 +1211,10 @@
         <v>0.2921192787540448</v>
       </c>
       <c r="C49">
-        <v>0.4188101764003093</v>
+        <v>0.4188101764003092</v>
       </c>
       <c r="D49">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C51">
-        <v>0.5016886059394927</v>
+        <v>0.5016886059394928</v>
       </c>
       <c r="D51">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1267,10 +1267,10 @@
         <v>0.2314292087413117</v>
       </c>
       <c r="C53">
-        <v>0.5043859448095898</v>
+        <v>0.5043859448095896</v>
       </c>
       <c r="D53">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
     </row>
     <row r="54" spans="1:4">

--- a/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
+++ b/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
@@ -550,13 +550,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.6741225709545154</v>
+        <v>0.6741225709545156</v>
       </c>
       <c r="C2">
         <v>0.3705533249609646</v>
       </c>
       <c r="D2">
-        <v>0.3035692459935508</v>
+        <v>0.303569245993551</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -570,7 +570,7 @@
         <v>0.4023740554348589</v>
       </c>
       <c r="D3">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -581,10 +581,10 @@
         <v>0.5218386559860035</v>
       </c>
       <c r="C4">
-        <v>0.522477060015217</v>
+        <v>0.5224770600152169</v>
       </c>
       <c r="D4">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -609,10 +609,10 @@
         <v>0.2972134155204859</v>
       </c>
       <c r="C6">
-        <v>0.5512673902348846</v>
+        <v>0.5512673902348847</v>
       </c>
       <c r="D6">
-        <v>-0.2540539747143987</v>
+        <v>-0.2540539747143988</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -626,7 +626,7 @@
         <v>0.5864783189261368</v>
       </c>
       <c r="D7">
-        <v>-0.3256873265123409</v>
+        <v>-0.325687326512341</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -637,10 +637,10 @@
         <v>0.5951237281573063</v>
       </c>
       <c r="C8">
-        <v>0.4041932886603293</v>
+        <v>0.4041932886603294</v>
       </c>
       <c r="D8">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969769</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -651,10 +651,10 @@
         <v>0.4417500520544824</v>
       </c>
       <c r="C9">
-        <v>0.466315729969719</v>
+        <v>0.4663157299697189</v>
       </c>
       <c r="D9">
-        <v>-0.02456567791523656</v>
+        <v>-0.02456567791523645</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -676,7 +676,7 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.1869441246967853</v>
+        <v>0.1869441246967854</v>
       </c>
       <c r="C11">
         <v>0.549050545884553</v>
@@ -693,10 +693,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12">
-        <v>0.6293909101742614</v>
+        <v>0.6293909101742613</v>
       </c>
       <c r="D12">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -735,10 +735,10 @@
         <v>0.3816235236497591</v>
       </c>
       <c r="C15">
-        <v>0.5485467523459437</v>
+        <v>0.5485467523459439</v>
       </c>
       <c r="D15">
-        <v>-0.1669232286961846</v>
+        <v>-0.1669232286961848</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -746,10 +746,10 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>0.2828138579726732</v>
+        <v>0.2828138579726733</v>
       </c>
       <c r="C16">
-        <v>0.4976624590930341</v>
+        <v>0.4976624590930342</v>
       </c>
       <c r="D16">
         <v>-0.2148486011203609</v>
@@ -763,10 +763,10 @@
         <v>0.2145524253023634</v>
       </c>
       <c r="C17">
-        <v>0.6001120644611281</v>
+        <v>0.600112064461128</v>
       </c>
       <c r="D17">
-        <v>-0.3855596391587647</v>
+        <v>-0.3855596391587646</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -805,10 +805,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20">
-        <v>0.5150045681354979</v>
+        <v>0.515004568135498</v>
       </c>
       <c r="D20">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -816,13 +816,13 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>0.7118486478275274</v>
+        <v>0.7118486478275275</v>
       </c>
       <c r="C21">
-        <v>0.4260034620050295</v>
+        <v>0.4260034620050296</v>
       </c>
       <c r="D21">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224979</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -850,7 +850,7 @@
         <v>0.4105420803197389</v>
       </c>
       <c r="D23">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927821</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -858,13 +858,13 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>0.2175554342042256</v>
+        <v>0.2175554342042255</v>
       </c>
       <c r="C24">
-        <v>0.5970724973798152</v>
+        <v>0.5970724973798153</v>
       </c>
       <c r="D24">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755898</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -875,10 +875,10 @@
         <v>0.547386166559502</v>
       </c>
       <c r="C25">
-        <v>0.4276290460083053</v>
+        <v>0.4276290460083051</v>
       </c>
       <c r="D25">
-        <v>0.1197571205511967</v>
+        <v>0.1197571205511969</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -886,10 +886,10 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>0.257369365075</v>
+        <v>0.2573693650749999</v>
       </c>
       <c r="C26">
-        <v>0.5837653200597678</v>
+        <v>0.5837653200597677</v>
       </c>
       <c r="D26">
         <v>-0.3263959549847678</v>
@@ -959,10 +959,10 @@
         <v>0.2726179454172194</v>
       </c>
       <c r="C31">
-        <v>0.5623898070994021</v>
+        <v>0.562389807099402</v>
       </c>
       <c r="D31">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821826</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -973,10 +973,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32">
-        <v>0.4830115777026097</v>
+        <v>0.4830115777026099</v>
       </c>
       <c r="D32">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -987,10 +987,10 @@
         <v>0.3328760832679651</v>
       </c>
       <c r="C33">
-        <v>0.4307152111273058</v>
+        <v>0.4307152111273059</v>
       </c>
       <c r="D33">
-        <v>-0.09783912785934062</v>
+        <v>-0.09783912785934074</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1012,10 +1012,10 @@
         <v>37</v>
       </c>
       <c r="B35">
-        <v>0.5394791234243426</v>
+        <v>0.5394791234243425</v>
       </c>
       <c r="C35">
-        <v>0.3857011247696835</v>
+        <v>0.3857011247696834</v>
       </c>
       <c r="D35">
         <v>0.1537779986546591</v>
@@ -1071,10 +1071,10 @@
         <v>0.4344379796487708</v>
       </c>
       <c r="C39">
-        <v>0.4334339392606038</v>
+        <v>0.4334339392606036</v>
       </c>
       <c r="D39">
-        <v>0.001004040388167093</v>
+        <v>0.001004040388167204</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1082,13 +1082,13 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>0.4653345520848203</v>
+        <v>0.4653345520848202</v>
       </c>
       <c r="C40">
-        <v>0.4840879159829741</v>
+        <v>0.4840879159829742</v>
       </c>
       <c r="D40">
-        <v>-0.0187533638981538</v>
+        <v>-0.01875336389815396</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1096,13 +1096,13 @@
         <v>43</v>
       </c>
       <c r="B41">
-        <v>0.6175455689522186</v>
+        <v>0.6175455689522185</v>
       </c>
       <c r="C41">
-        <v>0.3789088878499817</v>
+        <v>0.3789088878499818</v>
       </c>
       <c r="D41">
-        <v>0.2386366811022368</v>
+        <v>0.2386366811022366</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1141,10 +1141,10 @@
         <v>0.28232779787932</v>
       </c>
       <c r="C44">
-        <v>0.5720443857767511</v>
+        <v>0.572044385776751</v>
       </c>
       <c r="D44">
-        <v>-0.2897165878974311</v>
+        <v>-0.289716587897431</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1155,10 +1155,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C45">
-        <v>0.4177957142027762</v>
+        <v>0.4177957142027764</v>
       </c>
       <c r="D45">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1166,7 +1166,7 @@
         <v>48</v>
       </c>
       <c r="B46">
-        <v>0.3383392939535172</v>
+        <v>0.3383392939535171</v>
       </c>
       <c r="C46">
         <v>0.5106782077019681</v>
@@ -1183,10 +1183,10 @@
         <v>0.6041620014064532</v>
       </c>
       <c r="C47">
-        <v>0.3523044639392301</v>
+        <v>0.35230446393923</v>
       </c>
       <c r="D47">
-        <v>0.2518575374672231</v>
+        <v>0.2518575374672232</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1211,10 +1211,10 @@
         <v>0.2921192787540448</v>
       </c>
       <c r="C49">
-        <v>0.4188101764003092</v>
+        <v>0.4188101764003093</v>
       </c>
       <c r="D49">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462645</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C51">
-        <v>0.5016886059394928</v>
+        <v>0.5016886059394927</v>
       </c>
       <c r="D51">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060786</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1250,13 +1250,13 @@
         <v>54</v>
       </c>
       <c r="B52">
-        <v>0.4177702871705017</v>
+        <v>0.4177702871705016</v>
       </c>
       <c r="C52">
         <v>0.3917046326088484</v>
       </c>
       <c r="D52">
-        <v>0.02606565456165333</v>
+        <v>0.02606565456165322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1267,10 +1267,10 @@
         <v>0.2314292087413117</v>
       </c>
       <c r="C53">
-        <v>0.5043859448095896</v>
+        <v>0.5043859448095898</v>
       </c>
       <c r="D53">
-        <v>-0.272956736068278</v>
+        <v>-0.2729567360682781</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1309,7 +1309,7 @@
         <v>0.1845688251925361</v>
       </c>
       <c r="C56">
-        <v>0.6485514885399383</v>
+        <v>0.6485514885399384</v>
       </c>
       <c r="D56">
         <v>-0.4639826633474022</v>
@@ -1323,10 +1323,10 @@
         <v>0.2193986212219031</v>
       </c>
       <c r="C57">
-        <v>0.5675900717151439</v>
+        <v>0.5675900717151438</v>
       </c>
       <c r="D57">
-        <v>-0.3481914504932407</v>
+        <v>-0.3481914504932406</v>
       </c>
     </row>
     <row r="58" spans="1:4">

--- a/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
+++ b/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
@@ -553,10 +553,10 @@
         <v>0.6741225709545156</v>
       </c>
       <c r="C2">
-        <v>0.3705533249609646</v>
+        <v>0.3705533249609647</v>
       </c>
       <c r="D2">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935509</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -570,7 +570,7 @@
         <v>0.4023740554348589</v>
       </c>
       <c r="D3">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -581,10 +581,10 @@
         <v>0.5218386559860035</v>
       </c>
       <c r="C4">
-        <v>0.5224770600152169</v>
+        <v>0.522477060015217</v>
       </c>
       <c r="D4">
-        <v>-0.0006384040292133353</v>
+        <v>-0.0006384040292134463</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -598,7 +598,7 @@
         <v>0.3376764996165211</v>
       </c>
       <c r="D5">
-        <v>0.3490853798274803</v>
+        <v>0.3490853798274802</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -609,10 +609,10 @@
         <v>0.2972134155204859</v>
       </c>
       <c r="C6">
-        <v>0.5512673902348847</v>
+        <v>0.5512673902348848</v>
       </c>
       <c r="D6">
-        <v>-0.2540539747143988</v>
+        <v>-0.2540539747143989</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -676,13 +676,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.1869441246967854</v>
+        <v>0.1869441246967853</v>
       </c>
       <c r="C11">
-        <v>0.549050545884553</v>
+        <v>0.5490505458845529</v>
       </c>
       <c r="D11">
-        <v>-0.3621064211877677</v>
+        <v>-0.3621064211877676</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -693,10 +693,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12">
-        <v>0.6293909101742613</v>
+        <v>0.6293909101742614</v>
       </c>
       <c r="D12">
-        <v>-0.3785271549791803</v>
+        <v>-0.3785271549791804</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -707,10 +707,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13">
-        <v>0.6729153871303859</v>
+        <v>0.6729153871303858</v>
       </c>
       <c r="D13">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247937</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -721,10 +721,10 @@
         <v>0.2426910923322111</v>
       </c>
       <c r="C14">
-        <v>0.6427190948063813</v>
+        <v>0.6427190948063815</v>
       </c>
       <c r="D14">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741704</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -732,13 +732,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.3816235236497591</v>
+        <v>0.3816235236497592</v>
       </c>
       <c r="C15">
         <v>0.5485467523459439</v>
       </c>
       <c r="D15">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961847</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -760,10 +760,10 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>0.2145524253023634</v>
+        <v>0.2145524253023635</v>
       </c>
       <c r="C17">
-        <v>0.600112064461128</v>
+        <v>0.6001120644611281</v>
       </c>
       <c r="D17">
         <v>-0.3855596391587646</v>
@@ -774,13 +774,13 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>0.4296518046208666</v>
+        <v>0.4296518046208667</v>
       </c>
       <c r="C18">
-        <v>0.4945453559326177</v>
+        <v>0.4945453559326176</v>
       </c>
       <c r="D18">
-        <v>-0.06489355131175117</v>
+        <v>-0.06489355131175095</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -791,10 +791,10 @@
         <v>0.5237521220113416</v>
       </c>
       <c r="C19">
-        <v>0.4697918671910091</v>
+        <v>0.4697918671910092</v>
       </c>
       <c r="D19">
-        <v>0.05396025482033245</v>
+        <v>0.0539602548203324</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -819,10 +819,10 @@
         <v>0.7118486478275275</v>
       </c>
       <c r="C21">
-        <v>0.4260034620050296</v>
+        <v>0.4260034620050295</v>
       </c>
       <c r="D21">
-        <v>0.2858451858224979</v>
+        <v>0.285845185822498</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -833,10 +833,10 @@
         <v>0.3010798522307473</v>
       </c>
       <c r="C22">
-        <v>0.4999927429285567</v>
+        <v>0.4999927429285568</v>
       </c>
       <c r="D22">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -850,7 +850,7 @@
         <v>0.4105420803197389</v>
       </c>
       <c r="D23">
-        <v>0.1915672065927821</v>
+        <v>0.191567206592782</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -858,13 +858,13 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>0.2175554342042255</v>
+        <v>0.2175554342042256</v>
       </c>
       <c r="C24">
-        <v>0.5970724973798153</v>
+        <v>0.5970724973798152</v>
       </c>
       <c r="D24">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -903,10 +903,10 @@
         <v>0.1922848927634011</v>
       </c>
       <c r="C27">
-        <v>0.5332163798977593</v>
+        <v>0.5332163798977594</v>
       </c>
       <c r="D27">
-        <v>-0.3409314871343582</v>
+        <v>-0.3409314871343583</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -928,13 +928,13 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>0.3727681504267595</v>
+        <v>0.3727681504267594</v>
       </c>
       <c r="C29">
         <v>0.5189573803652675</v>
       </c>
       <c r="D29">
-        <v>-0.146189229938508</v>
+        <v>-0.1461892299385081</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -959,10 +959,10 @@
         <v>0.2726179454172194</v>
       </c>
       <c r="C31">
-        <v>0.562389807099402</v>
+        <v>0.5623898070994021</v>
       </c>
       <c r="D31">
-        <v>-0.2897718616821826</v>
+        <v>-0.2897718616821827</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -973,10 +973,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32">
-        <v>0.4830115777026099</v>
+        <v>0.4830115777026097</v>
       </c>
       <c r="D32">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -987,10 +987,10 @@
         <v>0.3328760832679651</v>
       </c>
       <c r="C33">
-        <v>0.4307152111273059</v>
+        <v>0.4307152111273058</v>
       </c>
       <c r="D33">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934068</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1015,10 +1015,10 @@
         <v>0.5394791234243425</v>
       </c>
       <c r="C35">
-        <v>0.3857011247696834</v>
+        <v>0.3857011247696835</v>
       </c>
       <c r="D35">
-        <v>0.1537779986546591</v>
+        <v>0.153777998654659</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1057,10 +1057,10 @@
         <v>0.2703323498637417</v>
       </c>
       <c r="C38">
-        <v>0.5056838147445358</v>
+        <v>0.5056838147445357</v>
       </c>
       <c r="D38">
-        <v>-0.2353514648807942</v>
+        <v>-0.2353514648807941</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1071,10 +1071,10 @@
         <v>0.4344379796487708</v>
       </c>
       <c r="C39">
-        <v>0.4334339392606036</v>
+        <v>0.4334339392606038</v>
       </c>
       <c r="D39">
-        <v>0.001004040388167204</v>
+        <v>0.001004040388167038</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1082,13 +1082,13 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>0.4653345520848202</v>
+        <v>0.4653345520848203</v>
       </c>
       <c r="C40">
         <v>0.4840879159829742</v>
       </c>
       <c r="D40">
-        <v>-0.01875336389815396</v>
+        <v>-0.01875336389815391</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1096,13 +1096,13 @@
         <v>43</v>
       </c>
       <c r="B41">
-        <v>0.6175455689522185</v>
+        <v>0.6175455689522186</v>
       </c>
       <c r="C41">
         <v>0.3789088878499818</v>
       </c>
       <c r="D41">
-        <v>0.2386366811022366</v>
+        <v>0.2386366811022367</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>0.3852882355996786</v>
       </c>
       <c r="D42">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1155,10 +1155,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C45">
-        <v>0.4177957142027764</v>
+        <v>0.4177957142027763</v>
       </c>
       <c r="D45">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1183,10 +1183,10 @@
         <v>0.6041620014064532</v>
       </c>
       <c r="C47">
-        <v>0.35230446393923</v>
+        <v>0.3523044639392302</v>
       </c>
       <c r="D47">
-        <v>0.2518575374672232</v>
+        <v>0.251857537467223</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1197,10 +1197,10 @@
         <v>0.3171438436680579</v>
       </c>
       <c r="C48">
-        <v>0.4237117552334944</v>
+        <v>0.4237117552334943</v>
       </c>
       <c r="D48">
-        <v>-0.1065679115654365</v>
+        <v>-0.1065679115654364</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1211,10 +1211,10 @@
         <v>0.2921192787540448</v>
       </c>
       <c r="C49">
-        <v>0.4188101764003093</v>
+        <v>0.4188101764003092</v>
       </c>
       <c r="D49">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1222,13 +1222,13 @@
         <v>52</v>
       </c>
       <c r="B50">
-        <v>0.4438010204861124</v>
+        <v>0.4438010204861125</v>
       </c>
       <c r="C50">
         <v>0.6094110466377607</v>
       </c>
       <c r="D50">
-        <v>-0.1656100261516483</v>
+        <v>-0.1656100261516482</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C51">
-        <v>0.5016886059394927</v>
+        <v>0.5016886059394928</v>
       </c>
       <c r="D51">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1281,10 +1281,10 @@
         <v>0.1990497928951852</v>
       </c>
       <c r="C54">
-        <v>0.652157489144949</v>
+        <v>0.6521574891449489</v>
       </c>
       <c r="D54">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1323,10 +1323,10 @@
         <v>0.2193986212219031</v>
       </c>
       <c r="C57">
-        <v>0.5675900717151438</v>
+        <v>0.5675900717151439</v>
       </c>
       <c r="D57">
-        <v>-0.3481914504932406</v>
+        <v>-0.3481914504932407</v>
       </c>
     </row>
     <row r="58" spans="1:4">

--- a/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
+++ b/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
@@ -553,10 +553,10 @@
         <v>0.6741225709545156</v>
       </c>
       <c r="C2">
-        <v>0.3705533249609647</v>
+        <v>0.3705533249609646</v>
       </c>
       <c r="D2">
-        <v>0.3035692459935509</v>
+        <v>0.303569245993551</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -567,10 +567,10 @@
         <v>0.3118390881364234</v>
       </c>
       <c r="C3">
-        <v>0.4023740554348589</v>
+        <v>0.402374055434859</v>
       </c>
       <c r="D3">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -595,10 +595,10 @@
         <v>0.6867618794440014</v>
       </c>
       <c r="C5">
-        <v>0.3376764996165211</v>
+        <v>0.337676499616521</v>
       </c>
       <c r="D5">
-        <v>0.3490853798274802</v>
+        <v>0.3490853798274803</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -609,10 +609,10 @@
         <v>0.2972134155204859</v>
       </c>
       <c r="C6">
-        <v>0.5512673902348848</v>
+        <v>0.5512673902348847</v>
       </c>
       <c r="D6">
-        <v>-0.2540539747143989</v>
+        <v>-0.2540539747143988</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -637,10 +637,10 @@
         <v>0.5951237281573063</v>
       </c>
       <c r="C8">
-        <v>0.4041932886603294</v>
+        <v>0.4041932886603293</v>
       </c>
       <c r="D8">
-        <v>0.1909304394969769</v>
+        <v>0.190930439496977</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -662,13 +662,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.5748115671389329</v>
+        <v>0.5748115671389328</v>
       </c>
       <c r="C10">
         <v>0.4689446995877983</v>
       </c>
       <c r="D10">
-        <v>0.1058668675511346</v>
+        <v>0.1058668675511344</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -676,10 +676,10 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.1869441246967853</v>
+        <v>0.1869441246967854</v>
       </c>
       <c r="C11">
-        <v>0.5490505458845529</v>
+        <v>0.549050545884553</v>
       </c>
       <c r="D11">
         <v>-0.3621064211877676</v>
@@ -693,10 +693,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12">
-        <v>0.6293909101742614</v>
+        <v>0.6293909101742613</v>
       </c>
       <c r="D12">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -707,10 +707,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13">
-        <v>0.6729153871303858</v>
+        <v>0.6729153871303859</v>
       </c>
       <c r="D13">
-        <v>-0.5012702603247937</v>
+        <v>-0.5012702603247938</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -721,10 +721,10 @@
         <v>0.2426910923322111</v>
       </c>
       <c r="C14">
-        <v>0.6427190948063815</v>
+        <v>0.6427190948063813</v>
       </c>
       <c r="D14">
-        <v>-0.4000280024741704</v>
+        <v>-0.4000280024741703</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -732,13 +732,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.3816235236497592</v>
+        <v>0.381623523649759</v>
       </c>
       <c r="C15">
         <v>0.5485467523459439</v>
       </c>
       <c r="D15">
-        <v>-0.1669232286961847</v>
+        <v>-0.1669232286961848</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -746,10 +746,10 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>0.2828138579726733</v>
+        <v>0.2828138579726732</v>
       </c>
       <c r="C16">
-        <v>0.4976624590930342</v>
+        <v>0.4976624590930341</v>
       </c>
       <c r="D16">
         <v>-0.2148486011203609</v>
@@ -774,13 +774,13 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>0.4296518046208667</v>
+        <v>0.4296518046208666</v>
       </c>
       <c r="C18">
         <v>0.4945453559326176</v>
       </c>
       <c r="D18">
-        <v>-0.06489355131175095</v>
+        <v>-0.06489355131175106</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -791,10 +791,10 @@
         <v>0.5237521220113416</v>
       </c>
       <c r="C19">
-        <v>0.4697918671910092</v>
+        <v>0.4697918671910091</v>
       </c>
       <c r="D19">
-        <v>0.0539602548203324</v>
+        <v>0.05396025482033245</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -805,10 +805,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20">
-        <v>0.515004568135498</v>
+        <v>0.5150045681354979</v>
       </c>
       <c r="D20">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -816,7 +816,7 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>0.7118486478275275</v>
+        <v>0.7118486478275274</v>
       </c>
       <c r="C21">
         <v>0.4260034620050295</v>
@@ -833,10 +833,10 @@
         <v>0.3010798522307473</v>
       </c>
       <c r="C22">
-        <v>0.4999927429285568</v>
+        <v>0.4999927429285567</v>
       </c>
       <c r="D22">
-        <v>-0.1989128906978095</v>
+        <v>-0.1989128906978094</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -844,13 +844,13 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>0.602109286912521</v>
+        <v>0.6021092869125209</v>
       </c>
       <c r="C23">
-        <v>0.4105420803197389</v>
+        <v>0.410542080319739</v>
       </c>
       <c r="D23">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927819</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -861,10 +861,10 @@
         <v>0.2175554342042256</v>
       </c>
       <c r="C24">
-        <v>0.5970724973798152</v>
+        <v>0.5970724973798153</v>
       </c>
       <c r="D24">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755897</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -872,13 +872,13 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>0.547386166559502</v>
+        <v>0.5473861665595021</v>
       </c>
       <c r="C25">
         <v>0.4276290460083051</v>
       </c>
       <c r="D25">
-        <v>0.1197571205511969</v>
+        <v>0.119757120551197</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -903,10 +903,10 @@
         <v>0.1922848927634011</v>
       </c>
       <c r="C27">
-        <v>0.5332163798977594</v>
+        <v>0.5332163798977593</v>
       </c>
       <c r="D27">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -931,10 +931,10 @@
         <v>0.3727681504267594</v>
       </c>
       <c r="C29">
-        <v>0.5189573803652675</v>
+        <v>0.5189573803652676</v>
       </c>
       <c r="D29">
-        <v>-0.1461892299385081</v>
+        <v>-0.1461892299385082</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -945,10 +945,10 @@
         <v>0.2292739130871298</v>
       </c>
       <c r="C30">
-        <v>0.4250474383301707</v>
+        <v>0.4250474383301708</v>
       </c>
       <c r="D30">
-        <v>-0.1957735252430409</v>
+        <v>-0.195773525243041</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -973,10 +973,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32">
-        <v>0.4830115777026097</v>
+        <v>0.4830115777026099</v>
       </c>
       <c r="D32">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -990,7 +990,7 @@
         <v>0.4307152111273058</v>
       </c>
       <c r="D33">
-        <v>-0.09783912785934068</v>
+        <v>-0.09783912785934062</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1012,7 +1012,7 @@
         <v>37</v>
       </c>
       <c r="B35">
-        <v>0.5394791234243425</v>
+        <v>0.5394791234243426</v>
       </c>
       <c r="C35">
         <v>0.3857011247696835</v>
@@ -1029,10 +1029,10 @@
         <v>0.2773539211539376</v>
       </c>
       <c r="C36">
-        <v>0.5754112849752648</v>
+        <v>0.5754112849752649</v>
       </c>
       <c r="D36">
-        <v>-0.2980573638213272</v>
+        <v>-0.2980573638213273</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1057,10 +1057,10 @@
         <v>0.2703323498637417</v>
       </c>
       <c r="C38">
-        <v>0.5056838147445357</v>
+        <v>0.5056838147445358</v>
       </c>
       <c r="D38">
-        <v>-0.2353514648807941</v>
+        <v>-0.2353514648807942</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1082,13 +1082,13 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>0.4653345520848203</v>
+        <v>0.4653345520848202</v>
       </c>
       <c r="C40">
         <v>0.4840879159829742</v>
       </c>
       <c r="D40">
-        <v>-0.01875336389815391</v>
+        <v>-0.01875336389815396</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>0.3852882355996786</v>
       </c>
       <c r="D42">
-        <v>0.176800648574842</v>
+        <v>0.1768006485748421</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1141,10 +1141,10 @@
         <v>0.28232779787932</v>
       </c>
       <c r="C44">
-        <v>0.572044385776751</v>
+        <v>0.5720443857767511</v>
       </c>
       <c r="D44">
-        <v>-0.289716587897431</v>
+        <v>-0.2897165878974311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1155,10 +1155,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C45">
-        <v>0.4177957142027763</v>
+        <v>0.4177957142027764</v>
       </c>
       <c r="D45">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1180,13 +1180,13 @@
         <v>49</v>
       </c>
       <c r="B47">
-        <v>0.6041620014064532</v>
+        <v>0.6041620014064533</v>
       </c>
       <c r="C47">
-        <v>0.3523044639392302</v>
+        <v>0.35230446393923</v>
       </c>
       <c r="D47">
-        <v>0.251857537467223</v>
+        <v>0.2518575374672233</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1222,10 +1222,10 @@
         <v>52</v>
       </c>
       <c r="B50">
-        <v>0.4438010204861125</v>
+        <v>0.4438010204861124</v>
       </c>
       <c r="C50">
-        <v>0.6094110466377607</v>
+        <v>0.6094110466377606</v>
       </c>
       <c r="D50">
         <v>-0.1656100261516482</v>
@@ -1253,10 +1253,10 @@
         <v>0.4177702871705016</v>
       </c>
       <c r="C52">
-        <v>0.3917046326088484</v>
+        <v>0.3917046326088485</v>
       </c>
       <c r="D52">
-        <v>0.02606565456165322</v>
+        <v>0.02606565456165311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1267,10 +1267,10 @@
         <v>0.2314292087413117</v>
       </c>
       <c r="C53">
-        <v>0.5043859448095898</v>
+        <v>0.5043859448095896</v>
       </c>
       <c r="D53">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1281,10 +1281,10 @@
         <v>0.1990497928951852</v>
       </c>
       <c r="C54">
-        <v>0.6521574891449489</v>
+        <v>0.652157489144949</v>
       </c>
       <c r="D54">
-        <v>-0.4531076962497637</v>
+        <v>-0.4531076962497638</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1309,7 +1309,7 @@
         <v>0.1845688251925361</v>
       </c>
       <c r="C56">
-        <v>0.6485514885399384</v>
+        <v>0.6485514885399383</v>
       </c>
       <c r="D56">
         <v>-0.4639826633474022</v>

--- a/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
+++ b/results/GSE186332/gse186332_frozen_recurrence_scores.xlsx
@@ -553,10 +553,10 @@
         <v>0.6741225709545156</v>
       </c>
       <c r="C2">
-        <v>0.3705533249609646</v>
+        <v>0.3705533249609645</v>
       </c>
       <c r="D2">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935511</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -567,10 +567,10 @@
         <v>0.3118390881364234</v>
       </c>
       <c r="C3">
-        <v>0.402374055434859</v>
+        <v>0.4023740554348589</v>
       </c>
       <c r="D3">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -581,10 +581,10 @@
         <v>0.5218386559860035</v>
       </c>
       <c r="C4">
-        <v>0.522477060015217</v>
+        <v>0.5224770600152169</v>
       </c>
       <c r="D4">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -595,7 +595,7 @@
         <v>0.6867618794440014</v>
       </c>
       <c r="C5">
-        <v>0.337676499616521</v>
+        <v>0.3376764996165211</v>
       </c>
       <c r="D5">
         <v>0.3490853798274803</v>
@@ -634,13 +634,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.5951237281573063</v>
+        <v>0.5951237281573062</v>
       </c>
       <c r="C8">
-        <v>0.4041932886603293</v>
+        <v>0.4041932886603294</v>
       </c>
       <c r="D8">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969768</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -651,10 +651,10 @@
         <v>0.4417500520544824</v>
       </c>
       <c r="C9">
-        <v>0.4663157299697189</v>
+        <v>0.4663157299697188</v>
       </c>
       <c r="D9">
-        <v>-0.02456567791523645</v>
+        <v>-0.02456567791523639</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -662,13 +662,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.5748115671389328</v>
+        <v>0.5748115671389329</v>
       </c>
       <c r="C10">
-        <v>0.4689446995877983</v>
+        <v>0.4689446995877984</v>
       </c>
       <c r="D10">
-        <v>0.1058668675511344</v>
+        <v>0.1058668675511345</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -676,13 +676,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.1869441246967854</v>
+        <v>0.1869441246967853</v>
       </c>
       <c r="C11">
         <v>0.549050545884553</v>
       </c>
       <c r="D11">
-        <v>-0.3621064211877676</v>
+        <v>-0.3621064211877677</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -707,10 +707,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13">
-        <v>0.6729153871303859</v>
+        <v>0.6729153871303858</v>
       </c>
       <c r="D13">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247936</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -721,10 +721,10 @@
         <v>0.2426910923322111</v>
       </c>
       <c r="C14">
-        <v>0.6427190948063813</v>
+        <v>0.6427190948063812</v>
       </c>
       <c r="D14">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741701</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -749,10 +749,10 @@
         <v>0.2828138579726732</v>
       </c>
       <c r="C16">
-        <v>0.4976624590930341</v>
+        <v>0.4976624590930342</v>
       </c>
       <c r="D16">
-        <v>-0.2148486011203609</v>
+        <v>-0.214848601120361</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -774,13 +774,13 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>0.4296518046208666</v>
+        <v>0.4296518046208667</v>
       </c>
       <c r="C18">
         <v>0.4945453559326176</v>
       </c>
       <c r="D18">
-        <v>-0.06489355131175106</v>
+        <v>-0.06489355131175095</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -788,13 +788,13 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>0.5237521220113416</v>
+        <v>0.5237521220113415</v>
       </c>
       <c r="C19">
         <v>0.4697918671910091</v>
       </c>
       <c r="D19">
-        <v>0.05396025482033245</v>
+        <v>0.05396025482033234</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -805,10 +805,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20">
-        <v>0.5150045681354979</v>
+        <v>0.515004568135498</v>
       </c>
       <c r="D20">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -816,13 +816,13 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>0.7118486478275274</v>
+        <v>0.7118486478275275</v>
       </c>
       <c r="C21">
         <v>0.4260034620050295</v>
       </c>
       <c r="D21">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224981</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -833,10 +833,10 @@
         <v>0.3010798522307473</v>
       </c>
       <c r="C22">
-        <v>0.4999927429285567</v>
+        <v>0.4999927429285569</v>
       </c>
       <c r="D22">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -844,13 +844,13 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>0.6021092869125209</v>
+        <v>0.602109286912521</v>
       </c>
       <c r="C23">
-        <v>0.410542080319739</v>
+        <v>0.4105420803197389</v>
       </c>
       <c r="D23">
-        <v>0.1915672065927819</v>
+        <v>0.191567206592782</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -858,13 +858,13 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>0.2175554342042256</v>
+        <v>0.2175554342042255</v>
       </c>
       <c r="C24">
         <v>0.5970724973798153</v>
       </c>
       <c r="D24">
-        <v>-0.3795170631755897</v>
+        <v>-0.3795170631755898</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -931,10 +931,10 @@
         <v>0.3727681504267594</v>
       </c>
       <c r="C29">
-        <v>0.5189573803652676</v>
+        <v>0.5189573803652675</v>
       </c>
       <c r="D29">
-        <v>-0.1461892299385082</v>
+        <v>-0.1461892299385081</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -959,10 +959,10 @@
         <v>0.2726179454172194</v>
       </c>
       <c r="C31">
-        <v>0.5623898070994021</v>
+        <v>0.5623898070994019</v>
       </c>
       <c r="D31">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821825</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -973,10 +973,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32">
-        <v>0.4830115777026099</v>
+        <v>0.4830115777026098</v>
       </c>
       <c r="D32">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1012,7 +1012,7 @@
         <v>37</v>
       </c>
       <c r="B35">
-        <v>0.5394791234243426</v>
+        <v>0.5394791234243425</v>
       </c>
       <c r="C35">
         <v>0.3857011247696835</v>
@@ -1029,10 +1029,10 @@
         <v>0.2773539211539376</v>
       </c>
       <c r="C36">
-        <v>0.5754112849752649</v>
+        <v>0.5754112849752648</v>
       </c>
       <c r="D36">
-        <v>-0.2980573638213273</v>
+        <v>-0.2980573638213272</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1099,7 +1099,7 @@
         <v>0.6175455689522186</v>
       </c>
       <c r="C41">
-        <v>0.3789088878499818</v>
+        <v>0.3789088878499819</v>
       </c>
       <c r="D41">
         <v>0.2386366811022367</v>
@@ -1116,7 +1116,7 @@
         <v>0.3852882355996786</v>
       </c>
       <c r="D42">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1141,10 +1141,10 @@
         <v>0.28232779787932</v>
       </c>
       <c r="C44">
-        <v>0.5720443857767511</v>
+        <v>0.572044385776751</v>
       </c>
       <c r="D44">
-        <v>-0.2897165878974311</v>
+        <v>-0.289716587897431</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1155,10 +1155,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C45">
-        <v>0.4177957142027764</v>
+        <v>0.4177957142027763</v>
       </c>
       <c r="D45">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1166,13 +1166,13 @@
         <v>48</v>
       </c>
       <c r="B46">
-        <v>0.3383392939535171</v>
+        <v>0.3383392939535172</v>
       </c>
       <c r="C46">
-        <v>0.5106782077019681</v>
+        <v>0.510678207701968</v>
       </c>
       <c r="D46">
-        <v>-0.172338913748451</v>
+        <v>-0.1723389137484508</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1180,13 +1180,13 @@
         <v>49</v>
       </c>
       <c r="B47">
-        <v>0.6041620014064533</v>
+        <v>0.6041620014064532</v>
       </c>
       <c r="C47">
-        <v>0.35230446393923</v>
+        <v>0.3523044639392302</v>
       </c>
       <c r="D47">
-        <v>0.2518575374672233</v>
+        <v>0.251857537467223</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1197,10 +1197,10 @@
         <v>0.3171438436680579</v>
       </c>
       <c r="C48">
-        <v>0.4237117552334943</v>
+        <v>0.4237117552334944</v>
       </c>
       <c r="D48">
-        <v>-0.1065679115654364</v>
+        <v>-0.1065679115654365</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1208,13 +1208,13 @@
         <v>51</v>
       </c>
       <c r="B49">
-        <v>0.2921192787540448</v>
+        <v>0.2921192787540449</v>
       </c>
       <c r="C49">
-        <v>0.4188101764003092</v>
+        <v>0.4188101764003091</v>
       </c>
       <c r="D49">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462642</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1225,10 +1225,10 @@
         <v>0.4438010204861124</v>
       </c>
       <c r="C50">
-        <v>0.6094110466377606</v>
+        <v>0.6094110466377607</v>
       </c>
       <c r="D50">
-        <v>-0.1656100261516482</v>
+        <v>-0.1656100261516483</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C51">
-        <v>0.5016886059394928</v>
+        <v>0.5016886059394929</v>
       </c>
       <c r="D51">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060808</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1253,10 +1253,10 @@
         <v>0.4177702871705016</v>
       </c>
       <c r="C52">
-        <v>0.3917046326088485</v>
+        <v>0.3917046326088484</v>
       </c>
       <c r="D52">
-        <v>0.02606565456165311</v>
+        <v>0.02606565456165327</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1281,10 +1281,10 @@
         <v>0.1990497928951852</v>
       </c>
       <c r="C54">
-        <v>0.652157489144949</v>
+        <v>0.6521574891449489</v>
       </c>
       <c r="D54">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1309,10 +1309,10 @@
         <v>0.1845688251925361</v>
       </c>
       <c r="C56">
-        <v>0.6485514885399383</v>
+        <v>0.6485514885399384</v>
       </c>
       <c r="D56">
-        <v>-0.4639826633474022</v>
+        <v>-0.4639826633474023</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1337,10 +1337,10 @@
         <v>0.2019181367419962</v>
       </c>
       <c r="C58">
-        <v>0.5318470851017671</v>
+        <v>0.531847085101767</v>
       </c>
       <c r="D58">
-        <v>-0.329928948359771</v>
+        <v>-0.3299289483597709</v>
       </c>
     </row>
   </sheetData>
